--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +492,76 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>001158</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SUB GENESIS R. COBOS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESPONSABLE INGRESA 3 CESTAS DE 26KG C/U EN SKU DE YUCA, SE VISUALIZA Y VERIFICA 3 CESTAS DE 2.6KG C/U. DIFERENCIA: 70.2KG </t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>161.46</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>INC_160808_0.png INC_160808_1.png INC_160808_2.png</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ID_20260602160808</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -57,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -420,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -489,11 +488,6 @@
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -557,11 +551,6 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>INC_160808_0.png INC_160808_1.png INC_160808_2.png</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ID_20260602160808</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -419,8 +419,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="37.69140625" customWidth="1" min="12" max="12"/>
+    <col width="49.3828125" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="82.765625" customWidth="1" min="15" max="15"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -485,6 +491,11 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>FOTO_INCIDENCIA</t>
         </is>
       </c>
@@ -548,7 +559,7 @@
           <t>RECUPERACIÓN</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>INC_160808_0.png INC_160808_1.png INC_160808_2.png</t>
         </is>

--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -56,7 +57,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,14 +420,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="37.69140625" customWidth="1" min="12" max="12"/>
-    <col width="49.3828125" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
-    <col width="82.765625" customWidth="1" min="15" max="15"/>
-  </cols>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -562,6 +557,71 @@
       <c r="N2" t="inlineStr">
         <is>
           <t>INC_160808_0.png INC_160808_1.png INC_160808_2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RUBROS SANARE C2, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0002409</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GERENTE JUAN V. MEZA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RECEPCIÓN SIN AUTORIZACIÓN DE CMF.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO E</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INICIA RECEPCIÓN SIN AUTORIZACIÓN PREVIA.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260604164608</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,6 +622,76 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>ID_20260604164608</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA LATIN FRUITS C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>LPCP ANGEL R. SECO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>RESPONSABLE NO CULMINÓ PROCESO DE FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260608074033</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>INC_074033_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,6 +692,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>INC_074033_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C.P.A BEJUMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LPCP ANGEL R. SECO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FISCALIZACIÓN A DESTIEMPO</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RESPONSABLE NO CULMINÓ PROCESO DE FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260608075012</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>INC_075012_0.png</t>
         </is>
       </c>
     </row>

--- a/cuadros/JUNIO/TUCACAS.xlsx
+++ b/cuadros/JUNIO/TUCACAS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,6 +762,76 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>INC_075012_0.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TUCACAS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAVA LUXOR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7250</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SUB GENESIS R. COBOS</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RESPONSABLE INGRESA TARA ERRADA, INGRESA TOBOS DE QUESO GUAYANES 3KG C/U. DANDO UNA DIFERENCIA DE 6KG</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260608081214</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>INC_081214_0.png INC_081214_1.png</t>
         </is>
       </c>
     </row>
